--- a/artfynd/A 37787-2025 artfynd.xlsx
+++ b/artfynd/A 37787-2025 artfynd.xlsx
@@ -2009,7 +2009,7 @@
         <v>127981664</v>
       </c>
       <c r="B14" t="n">
-        <v>4775</v>
+        <v>4777</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 37787-2025 artfynd.xlsx
+++ b/artfynd/A 37787-2025 artfynd.xlsx
@@ -2038,11 +2038,7 @@
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>

--- a/artfynd/A 37787-2025 artfynd.xlsx
+++ b/artfynd/A 37787-2025 artfynd.xlsx
@@ -2009,7 +2009,7 @@
         <v>127981664</v>
       </c>
       <c r="B14" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
